--- a/样例文件/中文/示例表格.xlsx
+++ b/样例文件/中文/示例表格.xlsx
@@ -1,38 +1,341 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="示例清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="示例清单" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="统计" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="97">
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>A-001</t>
+  </si>
+  <si>
+    <t>示例功能一</t>
+  </si>
+  <si>
+    <t>类别甲</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>用户A</t>
+  </si>
+  <si>
+    <t>A-002</t>
+  </si>
+  <si>
+    <t>示例功能二</t>
+  </si>
+  <si>
+    <t>类别乙</t>
+  </si>
+  <si>
+    <t>进行中</t>
+  </si>
+  <si>
+    <t>用户B</t>
+  </si>
+  <si>
+    <t>A-003</t>
+  </si>
+  <si>
+    <t>示例功能三</t>
+  </si>
+  <si>
+    <t>未开始</t>
+  </si>
+  <si>
+    <t>用户C</t>
+  </si>
+  <si>
+    <t>A-004</t>
+  </si>
+  <si>
+    <t>示例功能四</t>
+  </si>
+  <si>
+    <t>类别丙</t>
+  </si>
+  <si>
+    <t>用户D</t>
+  </si>
+  <si>
+    <t>A-005</t>
+  </si>
+  <si>
+    <t>示例功能5</t>
+  </si>
+  <si>
+    <t>A-006</t>
+  </si>
+  <si>
+    <t>示例功能6</t>
+  </si>
+  <si>
+    <t>A-007</t>
+  </si>
+  <si>
+    <t>示例功能7</t>
+  </si>
+  <si>
+    <t>A-008</t>
+  </si>
+  <si>
+    <t>示例功能8</t>
+  </si>
+  <si>
+    <t>A-009</t>
+  </si>
+  <si>
+    <t>示例功能9</t>
+  </si>
+  <si>
+    <t>A-010</t>
+  </si>
+  <si>
+    <t>示例功能10</t>
+  </si>
+  <si>
+    <t>A-011</t>
+  </si>
+  <si>
+    <t>示例功能11</t>
+  </si>
+  <si>
+    <t>A-012</t>
+  </si>
+  <si>
+    <t>示例功能12</t>
+  </si>
+  <si>
+    <t>A-013</t>
+  </si>
+  <si>
+    <t>示例功能13</t>
+  </si>
+  <si>
+    <t>A-014</t>
+  </si>
+  <si>
+    <t>示例功能14</t>
+  </si>
+  <si>
+    <t>A-015</t>
+  </si>
+  <si>
+    <t>示例功能15</t>
+  </si>
+  <si>
+    <t>用户C90</t>
+  </si>
+  <si>
+    <t>A-016</t>
+  </si>
+  <si>
+    <t>示例功能16</t>
+  </si>
+  <si>
+    <t>A-017</t>
+  </si>
+  <si>
+    <t>示例功能17</t>
+  </si>
+  <si>
+    <t>A-018</t>
+  </si>
+  <si>
+    <t>示例功能18</t>
+  </si>
+  <si>
+    <t>A-019</t>
+  </si>
+  <si>
+    <t>示例功能19</t>
+  </si>
+  <si>
+    <t>A-020</t>
+  </si>
+  <si>
+    <t>示例功能20</t>
+  </si>
+  <si>
+    <t>A-021</t>
+  </si>
+  <si>
+    <t>示例功能21</t>
+  </si>
+  <si>
+    <t>A-022</t>
+  </si>
+  <si>
+    <t>示例功能22</t>
+  </si>
+  <si>
+    <t>A-023</t>
+  </si>
+  <si>
+    <t>示例功能23</t>
+  </si>
+  <si>
+    <t>A-024</t>
+  </si>
+  <si>
+    <t>示例功能24</t>
+  </si>
+  <si>
+    <t>A-025</t>
+  </si>
+  <si>
+    <t>示例功能25</t>
+  </si>
+  <si>
+    <t>A-026</t>
+  </si>
+  <si>
+    <t>示例功能26</t>
+  </si>
+  <si>
+    <t>A-027</t>
+  </si>
+  <si>
+    <t>示例功能27</t>
+  </si>
+  <si>
+    <t>A-028</t>
+  </si>
+  <si>
+    <t>示例功能28</t>
+  </si>
+  <si>
+    <t>A-029</t>
+  </si>
+  <si>
+    <t>示例功能29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-030	示例功能30	类别乙	进行中	用户B
+A-031	示例功能31	类别甲	未开始	用户C
+A-032	示例功能32	类别丙	已完成	用户D
+A-033	示例功能33	类别甲	已完成	用户A
+A-034	示例功能34	类别乙	进行中	用户B
+A-035	示例功能35	类别甲	未开始	用户C
+A-036	示例功能36	类别丙	已完成	用户D
+A-037	示例功能37	类别甲	已完成	用户A
+A-038	示例功能38	类别乙	进行中	用户B
+A-039	示例功能39	类别甲	未开始	用户C</t>
+  </si>
+  <si>
+    <t>A-040</t>
+  </si>
+  <si>
+    <t>示例功能40</t>
+  </si>
+  <si>
+    <t>A-041</t>
+  </si>
+  <si>
+    <t>示例功能41</t>
+  </si>
+  <si>
+    <t>A-042</t>
+  </si>
+  <si>
+    <t>示例功能42</t>
+  </si>
+  <si>
+    <t>A-043</t>
+  </si>
+  <si>
+    <t>示例功能43</t>
+  </si>
+  <si>
+    <t>A-044</t>
+  </si>
+  <si>
+    <t>示例功能44</t>
+  </si>
+  <si>
+    <t>A-045</t>
+  </si>
+  <si>
+    <t>示例功能45</t>
+  </si>
+  <si>
+    <t>A-046</t>
+  </si>
+  <si>
+    <t>示例功能46</t>
+  </si>
+  <si>
+    <t>A-047</t>
+  </si>
+  <si>
+    <t>示例功能47</t>
+  </si>
+  <si>
+    <t>A-048</t>
+  </si>
+  <si>
+    <t>示例功能48</t>
+  </si>
+  <si>
+    <t>A-049</t>
+  </si>
+  <si>
+    <t>示例功能49</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,81 +359,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -418,154 +662,864 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>示例功能一</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>类别甲</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>用户A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>示例功能二</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>类别乙</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>用户B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>示例功能三</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>类别甲</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>用户C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>示例功能四</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>类别丙</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>用户D</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -574,65 +1528,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>类别甲</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>类别乙</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>类别丙</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>96</v>
       </c>
       <c r="B5">
         <f>SUM(B2:B4)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
